--- a/artfynd/A 36742-2024 artfynd.xlsx
+++ b/artfynd/A 36742-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90838952</v>
+        <v>90838966</v>
       </c>
       <c r="B2" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494831.0644882188</v>
+        <v>494755</v>
       </c>
       <c r="R2" t="n">
-        <v>7048298.982128511</v>
+        <v>7048463</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2019-08-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-08-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +764,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Grov asp (ca 40 - 50 cm dbh)</t>
+          <t>Granlågor (2 st)</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -806,15 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>90838981</v>
+        <v>90838952</v>
       </c>
       <c r="B3" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -846,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494720.1489685519</v>
+        <v>494831</v>
       </c>
       <c r="R3" t="n">
-        <v>7048418.149031652</v>
+        <v>7048299</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,19 +859,9 @@
           <t>2019-08-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-08-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,7 +880,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Klen asp</t>
+          <t>Grov asp (ca 40 - 50 cm dbh)</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -937,37 +907,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>90838965</v>
+        <v>90838981</v>
       </c>
       <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -977,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494755.0284726552</v>
+        <v>494720</v>
       </c>
       <c r="R4" t="n">
-        <v>7048463.099279184</v>
+        <v>7048418</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1010,19 +975,9 @@
           <t>2019-08-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-08-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,7 +996,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Granhögstubbe</t>
+          <t>Klen asp</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1061,137 +1016,6 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
-        <is>
-          <t>Kalkbarrskogar i Jämtlands län</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>90838966</v>
-      </c>
-      <c r="B5" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Bastubäcken-Västra Munkflohöjden, Jmt</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>494755.0284726552</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7048463.099279184</v>
-      </c>
-      <c r="S5" t="n">
-        <v>25</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Häggenås</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2019-08-19</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2019-08-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Skogar med hög bonitet</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Granlågor (2 st)</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
         <is>
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>

--- a/artfynd/A 36742-2024 artfynd.xlsx
+++ b/artfynd/A 36742-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90838966</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90838952</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,8 +1035,18 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90838981</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>